--- a/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w5_0s_h5_0s.xlsx
+++ b/data/analysis_gemini_2_5_flash_qwen2_audio/multimodal_event_eval_gemini_2_5_flash_qwen2_audio_w5_0s_h5_0s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>sound: engine(0-120), sound: tire_squeal(120-240), visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(24-96), visual: running(24-24), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-240)</t>
   </si>
   <si>
     <t>sound: horn(0-120), sound: impact(120-240)</t>
@@ -663,22 +666,22 @@
         <v>11</v>
       </c>
       <c r="B5">
+        <v>0.8</v>
+      </c>
+      <c r="C5">
+        <v>0.8</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0.4</v>
-      </c>
-      <c r="D5">
-        <v>0.571</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -831,7 +834,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -868,6 +871,23 @@
         <v>30</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -909,127 +929,699 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>31</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1041,39 +1633,39 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>19</v>
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1085,171 +1677,127 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1261,535 +1809,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
